--- a/model_outputs_paper1/TASK_B_LOS/LOS_3class_shap_top10.xlsx
+++ b/model_outputs_paper1/TASK_B_LOS/LOS_3class_shap_top10.xlsx
@@ -431,41 +431,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>num__rehab_month_adm</t>
+          <t>cat__icd_main_S1412</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03368904202367866</v>
+        <v>0.02100146845586857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>num__rehab_year_adm</t>
+          <t>num__high_comorbidity_flag</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0245196588763957</v>
+        <v>0.01969343043324584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cat__icd_main_S1412</t>
+          <t>num__icu_exposed</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00995279074849954</v>
+        <v>0.009131447386454758</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>num__high_comorbidity_flag</t>
+          <t>num__acute_MH_SUB_dis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0094245585361583</v>
+        <v>0.006736684035634713</v>
       </c>
     </row>
     <row r="6">
@@ -475,37 +475,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008745794860867013</v>
+        <v>0.005803877251602102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>num__acute_SCIM_TOTAL_dis</t>
+          <t>num__acute_MH_SUB_adm</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00838090273543524</v>
+        <v>0.004893541466424853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>num__n_icd_codes</t>
+          <t>num__acute_SP_SUB_adm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007336803746280802</v>
+        <v>0.004679205009768496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>num__acute_MH_SUB_dis</t>
+          <t>num__acute_SP_SUB_dis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00634185178855832</v>
+        <v>0.004665186114314182</v>
       </c>
     </row>
     <row r="10">
@@ -515,17 +515,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005878943999396685</v>
+        <v>0.004121201681108218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>num__acute_SP_SUB_adm</t>
+          <t>cat__icd_main_S1411</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.005075171568294531</v>
+        <v>0.003999140668581837</v>
       </c>
     </row>
   </sheetData>
